--- a/fixtures/jeju/timetables/bis/raw/405005.xlsx
+++ b/fixtures/jeju/timetables/bis/raw/405005.xlsx
@@ -6,10 +6,10 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="131 공항-동광양-봉개-교래-수망리-남원체육관" r:id="rId3" sheetId="1"/>
-    <sheet name="131 남원체육관-수망리-교래-봉개-동광양-공항" r:id="rId4" sheetId="2"/>
-    <sheet name="132 공항-제주시청-제대병원-교래-수망리-남원체육관" r:id="rId5" sheetId="3"/>
-    <sheet name="132 남원체육관-수망리-교래-제대병원-제주시청-공항" r:id="rId6" sheetId="4"/>
+    <sheet name="131 남원체육관-수망리-교래-봉개-동광양-공항" r:id="rId3" sheetId="1"/>
+    <sheet name="131 공항-동광양-봉개-교래-수망리-남원체육관" r:id="rId4" sheetId="2"/>
+    <sheet name="132 남원체육관-수망리-교래-제대병원-제주시청-공항" r:id="rId5" sheetId="3"/>
+    <sheet name="132 공항-제주시청-제대병원-교래-수망리-남원체육관" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
@@ -23,40 +23,411 @@
     <t>노선번호</t>
   </si>
   <si>
+    <t>금호리조트</t>
+  </si>
+  <si>
+    <t>남원읍사무소</t>
+  </si>
+  <si>
+    <t>수망리(수망가름)</t>
+  </si>
+  <si>
+    <t>교래사거리</t>
+  </si>
+  <si>
+    <t>제주대학교병원</t>
+  </si>
+  <si>
+    <t>봉개(대기고)</t>
+  </si>
+  <si>
+    <t>제주시청</t>
+  </si>
+  <si>
+    <t>동광양</t>
+  </si>
+  <si>
+    <t>제주터미널</t>
+  </si>
+  <si>
     <t>공항</t>
   </si>
   <si>
-    <t>제주터미널</t>
-  </si>
-  <si>
-    <t>동광양</t>
-  </si>
-  <si>
-    <t>제주시청</t>
-  </si>
-  <si>
-    <t>봉개(대기고)</t>
-  </si>
-  <si>
-    <t>제주대학교병원</t>
-  </si>
-  <si>
-    <t>교래사거리</t>
-  </si>
-  <si>
-    <t>수망리(수망가름)</t>
-  </si>
-  <si>
-    <t>남원읍사무소</t>
-  </si>
-  <si>
-    <t>금호리조트</t>
-  </si>
-  <si>
     <t>131</t>
   </si>
   <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>06:04</t>
+  </si>
+  <si>
+    <t>06:12</t>
+  </si>
+  <si>
+    <t>06:27</t>
+  </si>
+  <si>
     <t>X</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>06:57</t>
+  </si>
+  <si>
+    <t>07:06</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>07:24</t>
+  </si>
+  <si>
+    <t>07:32</t>
+  </si>
+  <si>
+    <t>07:47</t>
+  </si>
+  <si>
+    <t>08:06</t>
+  </si>
+  <si>
+    <t>08:18</t>
+  </si>
+  <si>
+    <t>08:24</t>
+  </si>
+  <si>
+    <t>08:33</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>08:34</t>
+  </si>
+  <si>
+    <t>08:42</t>
+  </si>
+  <si>
+    <t>08:57</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>09:27</t>
+  </si>
+  <si>
+    <t>09:36</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>09:44</t>
+  </si>
+  <si>
+    <t>09:52</t>
+  </si>
+  <si>
+    <t>10:07</t>
+  </si>
+  <si>
+    <t>10:26</t>
+  </si>
+  <si>
+    <t>10:38</t>
+  </si>
+  <si>
+    <t>10:44</t>
+  </si>
+  <si>
+    <t>10:53</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>10:54</t>
+  </si>
+  <si>
+    <t>11:02</t>
+  </si>
+  <si>
+    <t>11:17</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>11:47</t>
+  </si>
+  <si>
+    <t>11:56</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>12:04</t>
+  </si>
+  <si>
+    <t>12:12</t>
+  </si>
+  <si>
+    <t>12:27</t>
+  </si>
+  <si>
+    <t>12:46</t>
+  </si>
+  <si>
+    <t>12:58</t>
+  </si>
+  <si>
+    <t>13:04</t>
+  </si>
+  <si>
+    <t>13:13</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>13:14</t>
+  </si>
+  <si>
+    <t>13:22</t>
+  </si>
+  <si>
+    <t>13:37</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>14:07</t>
+  </si>
+  <si>
+    <t>14:16</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>14:24</t>
+  </si>
+  <si>
+    <t>14:32</t>
+  </si>
+  <si>
+    <t>14:47</t>
+  </si>
+  <si>
+    <t>15:06</t>
+  </si>
+  <si>
+    <t>15:18</t>
+  </si>
+  <si>
+    <t>15:24</t>
+  </si>
+  <si>
+    <t>15:33</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>15:34</t>
+  </si>
+  <si>
+    <t>15:42</t>
+  </si>
+  <si>
+    <t>15:57</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
+    <t>16:27</t>
+  </si>
+  <si>
+    <t>16:36</t>
+  </si>
+  <si>
+    <t>16:40</t>
+  </si>
+  <si>
+    <t>16:44</t>
+  </si>
+  <si>
+    <t>16:52</t>
+  </si>
+  <si>
+    <t>17:07</t>
+  </si>
+  <si>
+    <t>17:26</t>
+  </si>
+  <si>
+    <t>17:38</t>
+  </si>
+  <si>
+    <t>17:44</t>
+  </si>
+  <si>
+    <t>17:53</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>17:54</t>
+  </si>
+  <si>
+    <t>18:02</t>
+  </si>
+  <si>
+    <t>18:17</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>18:47</t>
+  </si>
+  <si>
+    <t>18:56</t>
+  </si>
+  <si>
+    <t>18:44</t>
+  </si>
+  <si>
+    <t>18:52</t>
+  </si>
+  <si>
+    <t>19:07</t>
+  </si>
+  <si>
+    <t>19:26</t>
+  </si>
+  <si>
+    <t>19:38</t>
+  </si>
+  <si>
+    <t>19:44</t>
+  </si>
+  <si>
+    <t>19:53</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>20:14</t>
+  </si>
+  <si>
+    <t>20:22</t>
+  </si>
+  <si>
+    <t>20:37</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>21:07</t>
+  </si>
+  <si>
+    <t>21:16</t>
+  </si>
+  <si>
+    <t>21:04</t>
+  </si>
+  <si>
+    <t>21:11</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>21:43</t>
+  </si>
+  <si>
+    <t>21:54</t>
+  </si>
+  <si>
+    <t>22:00
+(종료)</t>
+  </si>
+  <si>
+    <t>22:40
+(출발)</t>
+  </si>
+  <si>
+    <t>22:47</t>
+  </si>
+  <si>
+    <t>23:02</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>23:29
+(종료)</t>
+  </si>
+  <si>
+    <t>131번/132번</t>
+  </si>
+  <si>
+    <t>[131번] 금호리조트-남원체육관-남원환승정류장(남원읍사무소)-의귀초등학교-수망리(수망가름)-붉은오름
+            -교래사거리-제주돌문화공원-남조로검문소-봉개(대기고)-천수동-동광양-제주버스터미널-공항
+[132번] 금호리조트- 남원체육관-남원환승정류장(남원읍사무소)-의귀환승정류장(의귀초등학교)
+            -수망리(수망가름)-붉은오름-교래사거리-교래입구-제주국제대학교-제주대학교입구-제주대학교병원
+            -제주여중·고-중앙여고-법원-제주시청-제주버스터미널-공항</t>
+  </si>
+  <si>
+    <t>금호리조트(남원)→남조로→공항</t>
+  </si>
+  <si>
+    <t>[131번] 첫차 6:00, 막차(남원읍사무소 출발) 22:40, 배차간격 140~150분
+[132번] 첫차 7:20, 막차 21:00, 배차간격 120~140분, (동진여객 064-757-5714)</t>
+  </si>
+  <si>
+    <t>(시행일 : 2024.12.31.)</t>
   </si>
   <si>
     <t>6:00
@@ -81,12 +452,6 @@
     <t>06:59</t>
   </si>
   <si>
-    <t>132</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
     <t>07:03</t>
   </si>
   <si>
@@ -114,9 +479,6 @@
     <t>08:21</t>
   </si>
   <si>
-    <t>08:33</t>
-  </si>
-  <si>
     <t>08:46</t>
   </si>
   <si>
@@ -159,12 +521,6 @@
     <t>10:19</t>
   </si>
   <si>
-    <t>10:26</t>
-  </si>
-  <si>
-    <t>10:38</t>
-  </si>
-  <si>
     <t>10:51</t>
   </si>
   <si>
@@ -207,12 +563,6 @@
     <t>12:39</t>
   </si>
   <si>
-    <t>12:46</t>
-  </si>
-  <si>
-    <t>12:58</t>
-  </si>
-  <si>
     <t>13:11</t>
   </si>
   <si>
@@ -303,12 +653,6 @@
     <t>17:19</t>
   </si>
   <si>
-    <t>17:26</t>
-  </si>
-  <si>
-    <t>17:38</t>
-  </si>
-  <si>
     <t>17:51</t>
   </si>
   <si>
@@ -324,9 +668,6 @@
     <t>18:35</t>
   </si>
   <si>
-    <t>18:44</t>
-  </si>
-  <si>
     <t>18:48</t>
   </si>
   <si>
@@ -339,9 +680,6 @@
     <t>19:36</t>
   </si>
   <si>
-    <t>19:44</t>
-  </si>
-  <si>
     <t>19:48</t>
   </si>
   <si>
@@ -370,9 +708,6 @@
   </si>
   <si>
     <t>20:53</t>
-  </si>
-  <si>
-    <t>21:04</t>
   </si>
   <si>
     <t>21:26</t>
@@ -404,9 +739,6 @@
   <si>
     <t>22:35
 (종료)</t>
-  </si>
-  <si>
-    <t>131번/132번</t>
   </si>
   <si>
     <t>[[131번]  공항-제주버스터미널-동광양-천수동-봉개(대기고)-남조로검문소-제주돌문화공원-교래사거리
@@ -424,338 +756,6 @@
   </si>
   <si>
     <t>(시행일 : 2021.9.10)</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>06:04</t>
-  </si>
-  <si>
-    <t>06:12</t>
-  </si>
-  <si>
-    <t>06:27</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>06:57</t>
-  </si>
-  <si>
-    <t>07:06</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>07:24</t>
-  </si>
-  <si>
-    <t>07:32</t>
-  </si>
-  <si>
-    <t>07:47</t>
-  </si>
-  <si>
-    <t>08:06</t>
-  </si>
-  <si>
-    <t>08:18</t>
-  </si>
-  <si>
-    <t>08:24</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>08:34</t>
-  </si>
-  <si>
-    <t>08:42</t>
-  </si>
-  <si>
-    <t>08:57</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>09:27</t>
-  </si>
-  <si>
-    <t>09:36</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>09:44</t>
-  </si>
-  <si>
-    <t>09:52</t>
-  </si>
-  <si>
-    <t>10:07</t>
-  </si>
-  <si>
-    <t>10:44</t>
-  </si>
-  <si>
-    <t>10:53</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>10:54</t>
-  </si>
-  <si>
-    <t>11:02</t>
-  </si>
-  <si>
-    <t>11:17</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>11:47</t>
-  </si>
-  <si>
-    <t>11:56</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>12:04</t>
-  </si>
-  <si>
-    <t>12:12</t>
-  </si>
-  <si>
-    <t>12:27</t>
-  </si>
-  <si>
-    <t>13:04</t>
-  </si>
-  <si>
-    <t>13:13</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>13:14</t>
-  </si>
-  <si>
-    <t>13:22</t>
-  </si>
-  <si>
-    <t>13:37</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>14:07</t>
-  </si>
-  <si>
-    <t>14:16</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>14:24</t>
-  </si>
-  <si>
-    <t>14:32</t>
-  </si>
-  <si>
-    <t>14:47</t>
-  </si>
-  <si>
-    <t>15:06</t>
-  </si>
-  <si>
-    <t>15:18</t>
-  </si>
-  <si>
-    <t>15:24</t>
-  </si>
-  <si>
-    <t>15:33</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>15:34</t>
-  </si>
-  <si>
-    <t>15:42</t>
-  </si>
-  <si>
-    <t>15:57</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
-    <t>16:27</t>
-  </si>
-  <si>
-    <t>16:36</t>
-  </si>
-  <si>
-    <t>16:40</t>
-  </si>
-  <si>
-    <t>16:44</t>
-  </si>
-  <si>
-    <t>16:52</t>
-  </si>
-  <si>
-    <t>17:07</t>
-  </si>
-  <si>
-    <t>17:44</t>
-  </si>
-  <si>
-    <t>17:53</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>17:54</t>
-  </si>
-  <si>
-    <t>18:02</t>
-  </si>
-  <si>
-    <t>18:17</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>18:47</t>
-  </si>
-  <si>
-    <t>18:56</t>
-  </si>
-  <si>
-    <t>18:52</t>
-  </si>
-  <si>
-    <t>19:07</t>
-  </si>
-  <si>
-    <t>19:26</t>
-  </si>
-  <si>
-    <t>19:38</t>
-  </si>
-  <si>
-    <t>19:53</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>20:14</t>
-  </si>
-  <si>
-    <t>20:22</t>
-  </si>
-  <si>
-    <t>20:37</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>21:07</t>
-  </si>
-  <si>
-    <t>21:16</t>
-  </si>
-  <si>
-    <t>21:11</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>21:43</t>
-  </si>
-  <si>
-    <t>21:54</t>
-  </si>
-  <si>
-    <t>22:00
-(종료)</t>
-  </si>
-  <si>
-    <t>22:40
-(출발)</t>
-  </si>
-  <si>
-    <t>22:47</t>
-  </si>
-  <si>
-    <t>23:02</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>23:29
-(종료)</t>
-  </si>
-  <si>
-    <t>[131번] 금호리조트-남원체육관-남원환승정류장(남원읍사무소)-의귀초등학교-수망리(수망가름)-붉은오름
-            -교래사거리-제주돌문화공원-남조로검문소-봉개(대기고)-천수동-동광양-제주버스터미널-공항
-[132번] 금호리조트- 남원체육관-남원환승정류장(남원읍사무소)-의귀환승정류장(의귀초등학교)
-            -수망리(수망가름)-붉은오름-교래사거리-교래입구-제주국제대학교-제주대학교입구-제주대학교병원
-            -제주여중·고-중앙여고-법원-제주시청-제주버스터미널-공항</t>
-  </si>
-  <si>
-    <t>금호리조트(남원)→남조로→공항</t>
-  </si>
-  <si>
-    <t>[131번] 첫차 6:00, 막차(남원읍사무소 출발) 22:40, 배차간격 140~150분
-[132번] 첫차 7:20, 막차 21:00, 배차간격 120~140분, (동진여객 064-757-5714)</t>
-  </si>
-  <si>
-    <t>(시행일 : 2024.12.31.)</t>
   </si>
 </sst>
 </file>
@@ -1294,13 +1294,13 @@
   <sheetData>
     <row r="2" ht="100.0" customHeight="true">
       <c r="B2" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -1312,7 +1312,7 @@
     </row>
     <row r="3" ht="25.0" customHeight="true">
       <c r="B3" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -1342,7 +1342,7 @@
     </row>
     <row r="5" ht="25.0" customHeight="true">
       <c r="B5" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C5"/>
       <c r="D5"/>
@@ -1354,7 +1354,7 @@
       <c r="J5"/>
       <c r="K5"/>
       <c r="L5" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M5"/>
     </row>
@@ -1427,25 +1427,25 @@
         <v>15</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J8" s="12" t="s">
         <v>17</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M8" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" ht="40.0" customHeight="true">
@@ -1453,37 +1453,37 @@
         <v>2.0</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="L9" s="12" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M9" s="13" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" ht="40.0" customHeight="true">
@@ -1494,34 +1494,34 @@
         <v>12</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M10" s="13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" ht="40.0" customHeight="true">
@@ -1529,37 +1529,37 @@
         <v>4.0</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M11" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" ht="40.0" customHeight="true">
@@ -1570,34 +1570,34 @@
         <v>12</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M12" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" ht="40.0" customHeight="true">
@@ -1605,37 +1605,37 @@
         <v>6.0</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M13" s="13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" ht="40.0" customHeight="true">
@@ -1646,34 +1646,34 @@
         <v>12</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" ht="40.0" customHeight="true">
@@ -1681,37 +1681,37 @@
         <v>8.0</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M15" s="13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" ht="40.0" customHeight="true">
@@ -1722,34 +1722,34 @@
         <v>12</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="M16" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" ht="40.0" customHeight="true">
@@ -1757,37 +1757,37 @@
         <v>10.0</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M17" s="13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" ht="40.0" customHeight="true">
@@ -1798,34 +1798,34 @@
         <v>12</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>97</v>
+        <v>17</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M18" s="13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" ht="40.0" customHeight="true">
@@ -1833,37 +1833,37 @@
         <v>12.0</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>106</v>
+        <v>17</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M19" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" ht="40.0" customHeight="true">
@@ -1874,34 +1874,34 @@
         <v>12</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M20" s="13" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" ht="40.0" customHeight="true">
@@ -1909,37 +1909,37 @@
         <v>14.0</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>115</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>13</v>
+        <v>121</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>118</v>
+        <v>17</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M21" s="13" t="s">
-        <v>122</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" ht="40.0" customHeight="true">
@@ -1950,34 +1950,34 @@
         <v>12</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>123</v>
+        <v>17</v>
       </c>
       <c r="E22" s="15" t="s">
         <v>124</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>13</v>
+        <v>126</v>
       </c>
       <c r="H22" s="15" t="s">
-        <v>125</v>
+        <v>17</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>13</v>
+        <v>127</v>
       </c>
       <c r="J22" s="15" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="K22" s="15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L22" s="15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2013,7 +2013,7 @@
   <sheetData>
     <row r="2" ht="100.0" customHeight="true">
       <c r="B2" s="17" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C2" s="17"/>
       <c r="D2" s="17"/>
@@ -2137,7 +2137,7 @@
         <v>12</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>134</v>
+        <v>17</v>
       </c>
       <c r="E8" s="28" t="s">
         <v>135</v>
@@ -2146,25 +2146,25 @@
         <v>136</v>
       </c>
       <c r="G8" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="H8" s="28" t="s">
-        <v>13</v>
-      </c>
       <c r="I8" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="J8" s="28" t="s">
-        <v>13</v>
-      </c>
       <c r="K8" s="28" t="s">
-        <v>22</v>
+        <v>139</v>
       </c>
       <c r="L8" s="28" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M8" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" ht="40.0" customHeight="true">
@@ -2172,37 +2172,37 @@
         <v>2.0</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="F9" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="H9" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="G9" s="28" t="s">
+      <c r="J9" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="H9" s="28" t="s">
+      <c r="K9" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="I9" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="J9" s="28" t="s">
+      <c r="L9" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="K9" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="L9" s="28" t="s">
+      <c r="M9" s="29" t="s">
         <v>147</v>
-      </c>
-      <c r="M9" s="29" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="10" ht="40.0" customHeight="true">
@@ -2222,25 +2222,25 @@
         <v>150</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="H10" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="28" t="s">
+      <c r="K10" s="28" t="s">
         <v>152</v>
       </c>
-      <c r="J10" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="K10" s="28" t="s">
+      <c r="L10" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="L10" s="28" t="s">
+      <c r="M10" s="29" t="s">
         <v>154</v>
-      </c>
-      <c r="M10" s="29" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="11" ht="40.0" customHeight="true">
@@ -2248,37 +2248,37 @@
         <v>4.0</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="E11" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="F11" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="F11" s="28" t="s">
+      <c r="H11" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="G11" s="28" t="s">
+      <c r="J11" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="H11" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="I11" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="J11" s="28" t="s">
-        <v>48</v>
-      </c>
       <c r="K11" s="28" t="s">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="L11" s="28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M11" s="29" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" ht="40.0" customHeight="true">
@@ -2289,34 +2289,34 @@
         <v>12</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>164</v>
+        <v>43</v>
       </c>
       <c r="G12" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="28" t="s">
         <v>165</v>
       </c>
-      <c r="H12" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="28" t="s">
+      <c r="K12" s="28" t="s">
         <v>166</v>
       </c>
-      <c r="J12" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="K12" s="28" t="s">
+      <c r="L12" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="L12" s="28" t="s">
+      <c r="M12" s="29" t="s">
         <v>168</v>
-      </c>
-      <c r="M12" s="29" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="13" ht="40.0" customHeight="true">
@@ -2324,37 +2324,37 @@
         <v>6.0</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D13" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="E13" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="E13" s="28" t="s">
+      <c r="F13" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="H13" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="G13" s="28" t="s">
+      <c r="J13" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="H13" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="I13" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="J13" s="28" t="s">
-        <v>64</v>
-      </c>
       <c r="K13" s="28" t="s">
-        <v>13</v>
+        <v>174</v>
       </c>
       <c r="L13" s="28" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M13" s="29" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" ht="40.0" customHeight="true">
@@ -2365,34 +2365,34 @@
         <v>12</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>178</v>
+        <v>59</v>
       </c>
       <c r="G14" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="I14" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="28" t="s">
         <v>179</v>
       </c>
-      <c r="H14" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" s="28" t="s">
+      <c r="K14" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="J14" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="K14" s="28" t="s">
+      <c r="L14" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="L14" s="28" t="s">
+      <c r="M14" s="29" t="s">
         <v>182</v>
-      </c>
-      <c r="M14" s="29" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="15" ht="40.0" customHeight="true">
@@ -2400,37 +2400,37 @@
         <v>8.0</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="E15" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="E15" s="28" t="s">
+      <c r="F15" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="F15" s="28" t="s">
+      <c r="H15" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="28" t="s">
         <v>186</v>
       </c>
-      <c r="G15" s="28" t="s">
+      <c r="J15" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="H15" s="28" t="s">
+      <c r="K15" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="I15" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="J15" s="28" t="s">
+      <c r="L15" s="28" t="s">
         <v>189</v>
       </c>
-      <c r="K15" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="L15" s="28" t="s">
+      <c r="M15" s="29" t="s">
         <v>190</v>
-      </c>
-      <c r="M15" s="29" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="16" ht="40.0" customHeight="true">
@@ -2441,34 +2441,34 @@
         <v>12</v>
       </c>
       <c r="D16" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="E16" s="28" t="s">
         <v>192</v>
       </c>
-      <c r="E16" s="28" t="s">
+      <c r="F16" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="F16" s="28" t="s">
+      <c r="G16" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="G16" s="28" t="s">
+      <c r="I16" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="H16" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="I16" s="28" t="s">
+      <c r="K16" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="J16" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="K16" s="28" t="s">
+      <c r="L16" s="28" t="s">
         <v>197</v>
       </c>
-      <c r="L16" s="28" t="s">
+      <c r="M16" s="29" t="s">
         <v>198</v>
-      </c>
-      <c r="M16" s="29" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="17" ht="40.0" customHeight="true">
@@ -2476,37 +2476,37 @@
         <v>10.0</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D17" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="E17" s="28" t="s">
         <v>200</v>
       </c>
-      <c r="E17" s="28" t="s">
+      <c r="F17" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="F17" s="28" t="s">
+      <c r="H17" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="G17" s="28" t="s">
+      <c r="J17" s="28" t="s">
         <v>203</v>
       </c>
-      <c r="H17" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="I17" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="J17" s="28" t="s">
-        <v>96</v>
-      </c>
       <c r="K17" s="28" t="s">
-        <v>13</v>
+        <v>204</v>
       </c>
       <c r="L17" s="28" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M17" s="29" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" ht="40.0" customHeight="true">
@@ -2517,34 +2517,34 @@
         <v>12</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>208</v>
+        <v>91</v>
       </c>
       <c r="G18" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="I18" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="H18" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="I18" s="28" t="s">
+      <c r="K18" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="J18" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="K18" s="28" t="s">
+      <c r="L18" s="28" t="s">
         <v>211</v>
       </c>
-      <c r="L18" s="28" t="s">
+      <c r="M18" s="29" t="s">
         <v>212</v>
-      </c>
-      <c r="M18" s="29" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="19" ht="40.0" customHeight="true">
@@ -2552,34 +2552,34 @@
         <v>12.0</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D19" s="28" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F19" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" s="28" t="s">
         <v>214</v>
       </c>
-      <c r="G19" s="28" t="s">
+      <c r="H19" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" s="28" t="s">
         <v>215</v>
       </c>
-      <c r="H19" s="28" t="s">
+      <c r="J19" s="28" t="s">
         <v>216</v>
       </c>
-      <c r="I19" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="J19" s="28" t="s">
+      <c r="K19" s="28" t="s">
         <v>217</v>
       </c>
-      <c r="K19" s="28" t="s">
-        <v>13</v>
-      </c>
       <c r="L19" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M19" s="29" t="s">
         <v>218</v>
@@ -2599,28 +2599,28 @@
         <v>220</v>
       </c>
       <c r="F20" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="G20" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20" s="28" t="s">
+        <v>218</v>
+      </c>
+      <c r="I20" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="28" t="s">
         <v>221</v>
       </c>
-      <c r="G20" s="28" t="s">
+      <c r="K20" s="28" t="s">
         <v>222</v>
       </c>
-      <c r="H20" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" s="28" t="s">
+      <c r="L20" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="J20" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="K20" s="28" t="s">
+      <c r="M20" s="29" t="s">
         <v>224</v>
-      </c>
-      <c r="L20" s="28" t="s">
-        <v>225</v>
-      </c>
-      <c r="M20" s="29" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="21" ht="40.0" customHeight="true">
@@ -2628,37 +2628,37 @@
         <v>14.0</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E21" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="H21" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="F21" s="28" t="s">
-        <v>227</v>
-      </c>
-      <c r="G21" s="28" t="s">
+      <c r="J21" s="28" t="s">
         <v>228</v>
       </c>
-      <c r="H21" s="28" t="s">
+      <c r="K21" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="I21" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="J21" s="28" t="s">
+      <c r="L21" s="28" t="s">
         <v>230</v>
       </c>
-      <c r="K21" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="L21" s="28" t="s">
+      <c r="M21" s="29" t="s">
         <v>231</v>
-      </c>
-      <c r="M21" s="29" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="22" ht="40.0" customHeight="true">
@@ -2669,25 +2669,25 @@
         <v>12</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>13</v>
+        <v>232</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F22" s="31" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G22" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="31" t="s">
         <v>234</v>
       </c>
-      <c r="H22" s="31" t="s">
-        <v>13</v>
-      </c>
       <c r="I22" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="31" t="s">
         <v>235</v>
-      </c>
-      <c r="J22" s="31" t="s">
-        <v>13</v>
       </c>
       <c r="K22" s="31" t="s">
         <v>236</v>
@@ -2696,7 +2696,7 @@
         <v>237</v>
       </c>
       <c r="M22" s="32" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2732,13 +2732,13 @@
   <sheetData>
     <row r="2" ht="100.0" customHeight="true">
       <c r="B2" s="33" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C2" s="33"/>
       <c r="D2" s="33"/>
       <c r="E2" s="33"/>
       <c r="F2" s="35" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G2" s="33"/>
       <c r="H2" s="33"/>
@@ -2750,7 +2750,7 @@
     </row>
     <row r="3" ht="25.0" customHeight="true">
       <c r="B3" s="34" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -2780,7 +2780,7 @@
     </row>
     <row r="5" ht="25.0" customHeight="true">
       <c r="B5" s="37" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C5"/>
       <c r="D5"/>
@@ -2792,7 +2792,7 @@
       <c r="J5"/>
       <c r="K5"/>
       <c r="L5" s="39" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M5"/>
     </row>
@@ -2865,25 +2865,25 @@
         <v>15</v>
       </c>
       <c r="G8" s="44" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H8" s="44" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I8" s="44" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J8" s="44" t="s">
         <v>17</v>
       </c>
       <c r="K8" s="44" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M8" s="45" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" ht="40.0" customHeight="true">
@@ -2891,37 +2891,37 @@
         <v>2.0</v>
       </c>
       <c r="C9" s="44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E9" s="44" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F9" s="44" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G9" s="44" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H9" s="44" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="I9" s="44" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J9" s="44" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K9" s="44" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="L9" s="44" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M9" s="45" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" ht="40.0" customHeight="true">
@@ -2932,34 +2932,34 @@
         <v>12</v>
       </c>
       <c r="D10" s="44" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F10" s="44" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G10" s="44" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="H10" s="44" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="I10" s="44" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="J10" s="44" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="K10" s="44" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M10" s="45" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" ht="40.0" customHeight="true">
@@ -2967,37 +2967,37 @@
         <v>4.0</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F11" s="44" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H11" s="44" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="I11" s="44" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K11" s="44" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M11" s="45" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" ht="40.0" customHeight="true">
@@ -3008,34 +3008,34 @@
         <v>12</v>
       </c>
       <c r="D12" s="44" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F12" s="44" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G12" s="44" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="H12" s="44" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I12" s="44" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="J12" s="44" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="K12" s="44" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M12" s="45" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" ht="40.0" customHeight="true">
@@ -3043,37 +3043,37 @@
         <v>6.0</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F13" s="44" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="G13" s="44" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H13" s="44" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="I13" s="44" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="J13" s="44" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K13" s="44" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M13" s="45" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" ht="40.0" customHeight="true">
@@ -3084,34 +3084,34 @@
         <v>12</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F14" s="44" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G14" s="44" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="H14" s="44" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="I14" s="44" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="J14" s="44" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="K14" s="44" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L14" s="44" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M14" s="45" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" ht="40.0" customHeight="true">
@@ -3119,37 +3119,37 @@
         <v>8.0</v>
       </c>
       <c r="C15" s="44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F15" s="44" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="G15" s="44" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H15" s="44" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="J15" s="44" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K15" s="44" t="s">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M15" s="45" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" ht="40.0" customHeight="true">
@@ -3160,34 +3160,34 @@
         <v>12</v>
       </c>
       <c r="D16" s="44" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F16" s="44" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G16" s="44" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="H16" s="44" t="s">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="I16" s="44" t="s">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="J16" s="44" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="K16" s="44" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L16" s="44" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="M16" s="45" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" ht="40.0" customHeight="true">
@@ -3195,37 +3195,37 @@
         <v>10.0</v>
       </c>
       <c r="C17" s="44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D17" s="44" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F17" s="44" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H17" s="44" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="J17" s="44" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K17" s="44" t="s">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="L17" s="44" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M17" s="45" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" ht="40.0" customHeight="true">
@@ -3236,34 +3236,34 @@
         <v>12</v>
       </c>
       <c r="D18" s="44" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F18" s="44" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G18" s="44" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="H18" s="44" t="s">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="I18" s="44" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="J18" s="44" t="s">
-        <v>97</v>
+        <v>17</v>
       </c>
       <c r="K18" s="44" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L18" s="44" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M18" s="45" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" ht="40.0" customHeight="true">
@@ -3271,37 +3271,37 @@
         <v>12.0</v>
       </c>
       <c r="C19" s="44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D19" s="44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F19" s="44" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="G19" s="44" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H19" s="44" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="I19" s="44" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="J19" s="44" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K19" s="44" t="s">
-        <v>106</v>
+        <v>17</v>
       </c>
       <c r="L19" s="44" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M19" s="45" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" ht="40.0" customHeight="true">
@@ -3312,34 +3312,34 @@
         <v>12</v>
       </c>
       <c r="D20" s="44" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F20" s="44" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G20" s="44" t="s">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="H20" s="44" t="s">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c r="I20" s="44" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="J20" s="44" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="K20" s="44" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L20" s="44" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M20" s="45" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" ht="40.0" customHeight="true">
@@ -3347,37 +3347,37 @@
         <v>14.0</v>
       </c>
       <c r="C21" s="44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D21" s="44" t="s">
         <v>115</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F21" s="44" t="s">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="G21" s="44" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H21" s="44" t="s">
-        <v>13</v>
+        <v>121</v>
       </c>
       <c r="I21" s="44" t="s">
-        <v>118</v>
+        <v>17</v>
       </c>
       <c r="J21" s="44" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K21" s="44" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="L21" s="44" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M21" s="45" t="s">
-        <v>122</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" ht="40.0" customHeight="true">
@@ -3388,34 +3388,34 @@
         <v>12</v>
       </c>
       <c r="D22" s="47" t="s">
-        <v>123</v>
+        <v>17</v>
       </c>
       <c r="E22" s="47" t="s">
         <v>124</v>
       </c>
       <c r="F22" s="47" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G22" s="47" t="s">
-        <v>13</v>
+        <v>126</v>
       </c>
       <c r="H22" s="47" t="s">
-        <v>125</v>
+        <v>17</v>
       </c>
       <c r="I22" s="47" t="s">
-        <v>13</v>
+        <v>127</v>
       </c>
       <c r="J22" s="47" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="K22" s="47" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L22" s="47" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M22" s="48" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -3451,7 +3451,7 @@
   <sheetData>
     <row r="2" ht="100.0" customHeight="true">
       <c r="B2" s="49" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C2" s="49"/>
       <c r="D2" s="49"/>
@@ -3575,7 +3575,7 @@
         <v>12</v>
       </c>
       <c r="D8" s="60" t="s">
-        <v>134</v>
+        <v>17</v>
       </c>
       <c r="E8" s="60" t="s">
         <v>135</v>
@@ -3584,25 +3584,25 @@
         <v>136</v>
       </c>
       <c r="G8" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="60" t="s">
         <v>137</v>
       </c>
-      <c r="H8" s="60" t="s">
-        <v>13</v>
-      </c>
       <c r="I8" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="60" t="s">
         <v>138</v>
       </c>
-      <c r="J8" s="60" t="s">
-        <v>13</v>
-      </c>
       <c r="K8" s="60" t="s">
-        <v>22</v>
+        <v>139</v>
       </c>
       <c r="L8" s="60" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M8" s="61" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" ht="40.0" customHeight="true">
@@ -3610,37 +3610,37 @@
         <v>2.0</v>
       </c>
       <c r="C9" s="60" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" s="60" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="60" t="s">
         <v>141</v>
       </c>
-      <c r="E9" s="60" t="s">
+      <c r="F9" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="60" t="s">
         <v>142</v>
       </c>
-      <c r="F9" s="60" t="s">
+      <c r="H9" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="60" t="s">
         <v>143</v>
       </c>
-      <c r="G9" s="60" t="s">
+      <c r="J9" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="H9" s="60" t="s">
+      <c r="K9" s="60" t="s">
         <v>145</v>
       </c>
-      <c r="I9" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="J9" s="60" t="s">
+      <c r="L9" s="60" t="s">
         <v>146</v>
       </c>
-      <c r="K9" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="L9" s="60" t="s">
+      <c r="M9" s="61" t="s">
         <v>147</v>
-      </c>
-      <c r="M9" s="61" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="10" ht="40.0" customHeight="true">
@@ -3660,25 +3660,25 @@
         <v>150</v>
       </c>
       <c r="G10" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="60" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="60" t="s">
         <v>151</v>
       </c>
-      <c r="H10" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="60" t="s">
+      <c r="K10" s="60" t="s">
         <v>152</v>
       </c>
-      <c r="J10" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="K10" s="60" t="s">
+      <c r="L10" s="60" t="s">
         <v>153</v>
       </c>
-      <c r="L10" s="60" t="s">
+      <c r="M10" s="61" t="s">
         <v>154</v>
-      </c>
-      <c r="M10" s="61" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="11" ht="40.0" customHeight="true">
@@ -3686,37 +3686,37 @@
         <v>4.0</v>
       </c>
       <c r="C11" s="60" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" s="60" t="s">
+        <v>155</v>
+      </c>
+      <c r="E11" s="60" t="s">
         <v>156</v>
       </c>
-      <c r="E11" s="60" t="s">
+      <c r="F11" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="60" t="s">
         <v>157</v>
       </c>
-      <c r="F11" s="60" t="s">
+      <c r="H11" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="60" t="s">
         <v>158</v>
       </c>
-      <c r="G11" s="60" t="s">
+      <c r="J11" s="60" t="s">
         <v>159</v>
       </c>
-      <c r="H11" s="60" t="s">
-        <v>47</v>
-      </c>
-      <c r="I11" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="J11" s="60" t="s">
-        <v>48</v>
-      </c>
       <c r="K11" s="60" t="s">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="L11" s="60" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M11" s="61" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" ht="40.0" customHeight="true">
@@ -3727,34 +3727,34 @@
         <v>12</v>
       </c>
       <c r="D12" s="60" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E12" s="60" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F12" s="60" t="s">
-        <v>164</v>
+        <v>43</v>
       </c>
       <c r="G12" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="60" t="s">
         <v>165</v>
       </c>
-      <c r="H12" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="60" t="s">
+      <c r="K12" s="60" t="s">
         <v>166</v>
       </c>
-      <c r="J12" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="K12" s="60" t="s">
+      <c r="L12" s="60" t="s">
         <v>167</v>
       </c>
-      <c r="L12" s="60" t="s">
+      <c r="M12" s="61" t="s">
         <v>168</v>
-      </c>
-      <c r="M12" s="61" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="13" ht="40.0" customHeight="true">
@@ -3762,37 +3762,37 @@
         <v>6.0</v>
       </c>
       <c r="C13" s="60" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D13" s="60" t="s">
+        <v>169</v>
+      </c>
+      <c r="E13" s="60" t="s">
         <v>170</v>
       </c>
-      <c r="E13" s="60" t="s">
+      <c r="F13" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="60" t="s">
         <v>171</v>
       </c>
-      <c r="F13" s="60" t="s">
+      <c r="H13" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="60" t="s">
         <v>172</v>
       </c>
-      <c r="G13" s="60" t="s">
+      <c r="J13" s="60" t="s">
         <v>173</v>
       </c>
-      <c r="H13" s="60" t="s">
-        <v>63</v>
-      </c>
-      <c r="I13" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="J13" s="60" t="s">
-        <v>64</v>
-      </c>
       <c r="K13" s="60" t="s">
-        <v>13</v>
+        <v>174</v>
       </c>
       <c r="L13" s="60" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M13" s="61" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" ht="40.0" customHeight="true">
@@ -3803,34 +3803,34 @@
         <v>12</v>
       </c>
       <c r="D14" s="60" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E14" s="60" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F14" s="60" t="s">
-        <v>178</v>
+        <v>59</v>
       </c>
       <c r="G14" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="60" t="s">
+        <v>60</v>
+      </c>
+      <c r="I14" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="60" t="s">
         <v>179</v>
       </c>
-      <c r="H14" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" s="60" t="s">
+      <c r="K14" s="60" t="s">
         <v>180</v>
       </c>
-      <c r="J14" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="K14" s="60" t="s">
+      <c r="L14" s="60" t="s">
         <v>181</v>
       </c>
-      <c r="L14" s="60" t="s">
+      <c r="M14" s="61" t="s">
         <v>182</v>
-      </c>
-      <c r="M14" s="61" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="15" ht="40.0" customHeight="true">
@@ -3838,37 +3838,37 @@
         <v>8.0</v>
       </c>
       <c r="C15" s="60" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" s="60" t="s">
+        <v>183</v>
+      </c>
+      <c r="E15" s="60" t="s">
         <v>184</v>
       </c>
-      <c r="E15" s="60" t="s">
+      <c r="F15" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="60" t="s">
         <v>185</v>
       </c>
-      <c r="F15" s="60" t="s">
+      <c r="H15" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="60" t="s">
         <v>186</v>
       </c>
-      <c r="G15" s="60" t="s">
+      <c r="J15" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="H15" s="60" t="s">
+      <c r="K15" s="60" t="s">
         <v>188</v>
       </c>
-      <c r="I15" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="J15" s="60" t="s">
+      <c r="L15" s="60" t="s">
         <v>189</v>
       </c>
-      <c r="K15" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="L15" s="60" t="s">
+      <c r="M15" s="61" t="s">
         <v>190</v>
-      </c>
-      <c r="M15" s="61" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="16" ht="40.0" customHeight="true">
@@ -3879,34 +3879,34 @@
         <v>12</v>
       </c>
       <c r="D16" s="60" t="s">
+        <v>191</v>
+      </c>
+      <c r="E16" s="60" t="s">
         <v>192</v>
       </c>
-      <c r="E16" s="60" t="s">
+      <c r="F16" s="60" t="s">
         <v>193</v>
       </c>
-      <c r="F16" s="60" t="s">
+      <c r="G16" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" s="60" t="s">
         <v>194</v>
       </c>
-      <c r="G16" s="60" t="s">
+      <c r="I16" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="60" t="s">
         <v>195</v>
       </c>
-      <c r="H16" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="I16" s="60" t="s">
+      <c r="K16" s="60" t="s">
         <v>196</v>
       </c>
-      <c r="J16" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="K16" s="60" t="s">
+      <c r="L16" s="60" t="s">
         <v>197</v>
       </c>
-      <c r="L16" s="60" t="s">
+      <c r="M16" s="61" t="s">
         <v>198</v>
-      </c>
-      <c r="M16" s="61" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="17" ht="40.0" customHeight="true">
@@ -3914,37 +3914,37 @@
         <v>10.0</v>
       </c>
       <c r="C17" s="60" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D17" s="60" t="s">
+        <v>199</v>
+      </c>
+      <c r="E17" s="60" t="s">
         <v>200</v>
       </c>
-      <c r="E17" s="60" t="s">
+      <c r="F17" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="60" t="s">
         <v>201</v>
       </c>
-      <c r="F17" s="60" t="s">
+      <c r="H17" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" s="60" t="s">
         <v>202</v>
       </c>
-      <c r="G17" s="60" t="s">
+      <c r="J17" s="60" t="s">
         <v>203</v>
       </c>
-      <c r="H17" s="60" t="s">
-        <v>95</v>
-      </c>
-      <c r="I17" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="J17" s="60" t="s">
-        <v>96</v>
-      </c>
       <c r="K17" s="60" t="s">
-        <v>13</v>
+        <v>204</v>
       </c>
       <c r="L17" s="60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M17" s="61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" ht="40.0" customHeight="true">
@@ -3955,34 +3955,34 @@
         <v>12</v>
       </c>
       <c r="D18" s="60" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E18" s="60" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F18" s="60" t="s">
-        <v>208</v>
+        <v>91</v>
       </c>
       <c r="G18" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="60" t="s">
+        <v>92</v>
+      </c>
+      <c r="I18" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="60" t="s">
         <v>209</v>
       </c>
-      <c r="H18" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="I18" s="60" t="s">
+      <c r="K18" s="60" t="s">
         <v>210</v>
       </c>
-      <c r="J18" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="K18" s="60" t="s">
+      <c r="L18" s="60" t="s">
         <v>211</v>
       </c>
-      <c r="L18" s="60" t="s">
+      <c r="M18" s="61" t="s">
         <v>212</v>
-      </c>
-      <c r="M18" s="61" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="19" ht="40.0" customHeight="true">
@@ -3990,34 +3990,34 @@
         <v>12.0</v>
       </c>
       <c r="C19" s="60" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D19" s="60" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E19" s="60" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F19" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" s="60" t="s">
         <v>214</v>
       </c>
-      <c r="G19" s="60" t="s">
+      <c r="H19" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" s="60" t="s">
         <v>215</v>
       </c>
-      <c r="H19" s="60" t="s">
+      <c r="J19" s="60" t="s">
         <v>216</v>
       </c>
-      <c r="I19" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="J19" s="60" t="s">
+      <c r="K19" s="60" t="s">
         <v>217</v>
       </c>
-      <c r="K19" s="60" t="s">
-        <v>13</v>
-      </c>
       <c r="L19" s="60" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M19" s="61" t="s">
         <v>218</v>
@@ -4037,28 +4037,28 @@
         <v>220</v>
       </c>
       <c r="F20" s="60" t="s">
+        <v>217</v>
+      </c>
+      <c r="G20" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20" s="60" t="s">
+        <v>218</v>
+      </c>
+      <c r="I20" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="60" t="s">
         <v>221</v>
       </c>
-      <c r="G20" s="60" t="s">
+      <c r="K20" s="60" t="s">
         <v>222</v>
       </c>
-      <c r="H20" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" s="60" t="s">
+      <c r="L20" s="60" t="s">
         <v>223</v>
       </c>
-      <c r="J20" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="K20" s="60" t="s">
+      <c r="M20" s="61" t="s">
         <v>224</v>
-      </c>
-      <c r="L20" s="60" t="s">
-        <v>225</v>
-      </c>
-      <c r="M20" s="61" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="21" ht="40.0" customHeight="true">
@@ -4066,37 +4066,37 @@
         <v>14.0</v>
       </c>
       <c r="C21" s="60" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D21" s="60" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E21" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="F21" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" s="60" t="s">
+        <v>227</v>
+      </c>
+      <c r="H21" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="60" t="s">
         <v>118</v>
       </c>
-      <c r="F21" s="60" t="s">
-        <v>227</v>
-      </c>
-      <c r="G21" s="60" t="s">
+      <c r="J21" s="60" t="s">
         <v>228</v>
       </c>
-      <c r="H21" s="60" t="s">
+      <c r="K21" s="60" t="s">
         <v>229</v>
       </c>
-      <c r="I21" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="J21" s="60" t="s">
+      <c r="L21" s="60" t="s">
         <v>230</v>
       </c>
-      <c r="K21" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="L21" s="60" t="s">
+      <c r="M21" s="61" t="s">
         <v>231</v>
-      </c>
-      <c r="M21" s="61" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="22" ht="40.0" customHeight="true">
@@ -4107,25 +4107,25 @@
         <v>12</v>
       </c>
       <c r="D22" s="63" t="s">
-        <v>13</v>
+        <v>232</v>
       </c>
       <c r="E22" s="63" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F22" s="63" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G22" s="63" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="63" t="s">
         <v>234</v>
       </c>
-      <c r="H22" s="63" t="s">
-        <v>13</v>
-      </c>
       <c r="I22" s="63" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="63" t="s">
         <v>235</v>
-      </c>
-      <c r="J22" s="63" t="s">
-        <v>13</v>
       </c>
       <c r="K22" s="63" t="s">
         <v>236</v>
@@ -4134,7 +4134,7 @@
         <v>237</v>
       </c>
       <c r="M22" s="64" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
